--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\COPEC Projects\Dashboard precios EDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E332C79-803D-4F63-9CD8-77E536BD9A0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4339863-E5E1-4DA4-B84B-D393CDCFF500}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8010" activeTab="1" xr2:uid="{9E9E8C97-F897-498C-ABE3-FC758CD73A4D}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="BD Final" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BD Final'!$A$1:$U$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BD Final'!$A$1:$U$108</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="14"/>
   <pivotCaches>
-    <pivotCache cacheId="127" r:id="rId3"/>
-    <pivotCache cacheId="128" r:id="rId4"/>
+    <pivotCache cacheId="172" r:id="rId3"/>
+    <pivotCache cacheId="173" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="363">
   <si>
     <t>Periodo Precio</t>
   </si>
@@ -1116,6 +1116,12 @@
   </si>
   <si>
     <t>PERQUENCO</t>
+  </si>
+  <si>
+    <t>HUENTELAUQUEN</t>
+  </si>
+  <si>
+    <t>Huentelauquen</t>
   </si>
 </sst>
 </file>
@@ -1307,26 +1313,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1527,6 +1513,26 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1657,7 +1663,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Matias Raymundo Lineros Sandoval" refreshedDate="46203.754170486114" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="112" xr:uid="{3108BFF8-D622-49A9-9750-608FEEF49873}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:U113" sheet="BD Final"/>
+    <worksheetSource ref="A1:U108" sheet="BD Final"/>
   </cacheSource>
   <cacheFields count="21">
     <cacheField name="Tiene precio?" numFmtId="0">
@@ -6450,7 +6456,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9D49B51-918C-457D-B33C-3745ACEC6F18}" name="TablaDinámica5" cacheId="128" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9D49B51-918C-457D-B33C-3745ACEC6F18}" name="TablaDinámica5" cacheId="173" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A45:H135" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
@@ -7046,10 +7052,10 @@
     <dataField name="Promedio de Precio Tótem (C/IVA) ($/L)" fld="18" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -7072,7 +7078,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC45BB93-3292-4D4B-94AA-8DD3EB53AFAD}" name="TablaDinámica1" cacheId="127" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC45BB93-3292-4D4B-94AA-8DD3EB53AFAD}" name="TablaDinámica1" cacheId="172" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A141:G160" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
@@ -7343,7 +7349,7 @@
     <dataField name="Promedio de Precio Tótem (C/IVA) ($/L)" fld="16" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -7360,7 +7366,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1A2F10-8AF0-44F2-8761-62B039B0CA6F}" name="TablaDinámica3" cacheId="128" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1A2F10-8AF0-44F2-8761-62B039B0CA6F}" name="TablaDinámica3" cacheId="173" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G21" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="21">
     <pivotField axis="axisPage" compact="0" outline="0" subtotalTop="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -7652,10 +7658,10 @@
     <dataField name="Promedio de Precio Tótem (C/IVA) ($/L)" fld="18" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="5">
+    <format dxfId="25">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="24">
       <pivotArea field="5" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="5" count="3" selected="0">
@@ -7666,7 +7672,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="23">
       <pivotArea field="5" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="5" count="1" selected="0">
@@ -12175,82 +12181,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H6:H21">
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I21">
-    <cfRule type="cellIs" dxfId="23" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47:I133">
-    <cfRule type="cellIs" dxfId="21" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47:J133">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47:K132">
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47:L132">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H143:H161">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I143:I161">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J143:J161">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K143:K161">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12260,6 +12266,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId5"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -12268,7 +12277,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:U113"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.6640625" style="22"/>
@@ -19322,22 +19331,22 @@
         <v>27</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E109" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>306</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>76</v>
+        <v>361</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>305</v>
       </c>
       <c r="I109" t="s">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>305</v>
@@ -19366,8 +19375,8 @@
       <c r="R109" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="S109" s="3">
-        <v>897</v>
+      <c r="S109" s="20">
+        <v>0</v>
       </c>
       <c r="T109" s="3" t="s">
         <v>305</v>
@@ -19376,271 +19385,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>356</v>
-      </c>
-      <c r="B110">
-        <v>202606</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E110" s="1">
-        <v>7</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I110" t="s">
-        <v>327</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="P110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="R110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="S110" s="20">
-        <v>810</v>
-      </c>
-      <c r="T110" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="U110" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>356</v>
-      </c>
-      <c r="B111">
-        <v>202606</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E111" s="1">
-        <v>9</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I111" t="s">
-        <v>325</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="O111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="P111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="R111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="S111" s="20">
-        <v>828</v>
-      </c>
-      <c r="T111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="U111" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A112" t="str">
-        <f t="shared" ref="A110:A113" si="0">+IF(S112&lt;&gt;0,"si","no")</f>
-        <v>si</v>
-      </c>
-      <c r="B112">
-        <v>202606</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E112" s="1">
-        <v>7</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I112" t="s">
-        <v>327</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="O112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="P112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="R112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="S112" s="20">
-        <v>810</v>
-      </c>
-      <c r="T112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="U112" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A113" t="str">
-        <f t="shared" si="0"/>
-        <v>si</v>
-      </c>
-      <c r="B113">
-        <v>202606</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E113" s="1">
-        <v>9</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I113" t="s">
-        <v>325</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="O113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="P113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="R113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="S113" s="20">
-        <v>828</v>
-      </c>
-      <c r="T113" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="U113" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U113" xr:uid="{868BBEE7-4A6F-40EC-9605-DE44E330ADA7}"/>
+  <autoFilter ref="A1:U108" xr:uid="{A17D80BF-9E8E-4EB1-948F-6AC5EB59E316}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId2"/>
+  </customProperties>
 </worksheet>
 </file>